--- a/artfynd/A 33659-2023 artfynd.xlsx
+++ b/artfynd/A 33659-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33659-2023 artfynd.xlsx
+++ b/artfynd/A 33659-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112360956</v>
+        <v>112380266</v>
       </c>
       <c r="B2" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518056</v>
+        <v>518031</v>
       </c>
       <c r="R2" t="n">
-        <v>7181359</v>
+        <v>7181142</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,12 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,6 +771,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -798,15 +808,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112360935</v>
+        <v>112382054</v>
       </c>
       <c r="B3" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,38 +819,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissön, Väster-Rissön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517977</v>
+        <v>517832</v>
       </c>
       <c r="R3" t="n">
-        <v>7181358</v>
+        <v>7181296</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,12 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,6 +904,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -921,15 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112359858</v>
+        <v>112377569</v>
       </c>
       <c r="B4" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,38 +952,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissön, Väster-Rissön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518150</v>
+        <v>518414</v>
       </c>
       <c r="R4" t="n">
-        <v>7181081</v>
+        <v>7181238</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,12 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,6 +1037,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1044,15 +1074,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112360699</v>
+        <v>112381914</v>
       </c>
       <c r="B5" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,38 +1085,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517871</v>
+        <v>517911</v>
       </c>
       <c r="R5" t="n">
-        <v>7181203</v>
+        <v>7181235</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,7 +1145,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,12 +1155,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,6 +1170,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1167,15 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112360782</v>
+        <v>112382121</v>
       </c>
       <c r="B6" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,38 +1218,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517898</v>
+        <v>517844</v>
       </c>
       <c r="R6" t="n">
-        <v>7181203</v>
+        <v>7181358</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,7 +1278,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,12 +1288,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,6 +1303,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1290,54 +1340,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112360882</v>
+        <v>112377185</v>
       </c>
       <c r="B7" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517963</v>
+        <v>518346</v>
       </c>
       <c r="R7" t="n">
-        <v>7181358</v>
+        <v>7181224</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,7 +1411,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1376,12 +1421,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,6 +1436,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1413,54 +1473,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112360600</v>
+        <v>112379312</v>
       </c>
       <c r="B8" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517911</v>
+        <v>518066</v>
       </c>
       <c r="R8" t="n">
-        <v>7181235</v>
+        <v>7181134</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1489,7 +1544,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1499,12 +1554,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,6 +1569,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1536,15 +1606,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112361027</v>
+        <v>112359401</v>
       </c>
       <c r="B9" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,14 +1638,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518175</v>
+        <v>518242</v>
       </c>
       <c r="R9" t="n">
-        <v>7181267</v>
+        <v>7181298</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1612,7 +1677,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1622,12 +1687,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,15 +1724,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112360000</v>
+        <v>112359584</v>
       </c>
       <c r="B10" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,14 +1756,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517952</v>
+        <v>518347</v>
       </c>
       <c r="R10" t="n">
-        <v>7181173</v>
+        <v>7181299</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1735,7 +1795,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1745,12 +1805,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1782,15 +1842,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112359874</v>
+        <v>112359677</v>
       </c>
       <c r="B11" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,14 +1874,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518071</v>
+        <v>518387</v>
       </c>
       <c r="R11" t="n">
-        <v>7181080</v>
+        <v>7181237</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1858,7 +1913,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,7 +1923,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1905,15 +1960,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112360565</v>
+        <v>112359774</v>
       </c>
       <c r="B12" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,14 +1992,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517939</v>
+        <v>518269</v>
       </c>
       <c r="R12" t="n">
-        <v>7181204</v>
+        <v>7181175</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1981,7 +2031,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1991,12 +2041,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Både färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2028,15 +2078,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112381644</v>
+        <v>112359858</v>
       </c>
       <c r="B13" t="n">
-        <v>89671</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2044,38 +2089,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissön), Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517965</v>
+        <v>518150</v>
       </c>
       <c r="R13" t="n">
-        <v>7181173</v>
+        <v>7181081</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2104,7 +2149,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2114,7 +2159,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2129,26 +2179,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2166,15 +2196,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112375515</v>
+        <v>112359874</v>
       </c>
       <c r="B14" t="n">
-        <v>77745</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,40 +2207,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster-Rissön, Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518198</v>
+        <v>518071</v>
       </c>
       <c r="R14" t="n">
-        <v>7181286</v>
+        <v>7181080</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2242,18 +2265,32 @@
           <t>2023-09-26</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-09-26</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2277,15 +2314,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112382121</v>
+        <v>112360000</v>
       </c>
       <c r="B15" t="n">
-        <v>89649</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,38 +2325,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517844</v>
+        <v>517952</v>
       </c>
       <c r="R15" t="n">
-        <v>7181358</v>
+        <v>7181173</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2353,7 +2385,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2363,7 +2395,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,26 +2415,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2415,15 +2432,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112375371</v>
+        <v>112360565</v>
       </c>
       <c r="B16" t="n">
-        <v>77745</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2431,40 +2443,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Rissön, Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517859</v>
+        <v>517938</v>
       </c>
       <c r="R16" t="n">
-        <v>7181249</v>
+        <v>7181203</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2491,18 +2501,32 @@
           <t>2023-09-26</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-09-26</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Både färska och äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2526,15 +2550,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112375286</v>
+        <v>112360600</v>
       </c>
       <c r="B17" t="n">
-        <v>77745</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,40 +2561,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster-Rissön, Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518066</v>
+        <v>517911</v>
       </c>
       <c r="R17" t="n">
-        <v>7181133</v>
+        <v>7181235</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2602,18 +2619,32 @@
           <t>2023-09-26</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-09-26</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2637,15 +2668,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112375476</v>
+        <v>112360699</v>
       </c>
       <c r="B18" t="n">
-        <v>77745</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2653,40 +2679,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster-Rissön, Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517971</v>
+        <v>517872</v>
       </c>
       <c r="R18" t="n">
-        <v>7181355</v>
+        <v>7181203</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2713,18 +2737,32 @@
           <t>2023-09-26</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-09-26</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2748,15 +2786,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112375418</v>
+        <v>112360782</v>
       </c>
       <c r="B19" t="n">
-        <v>77745</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,40 +2797,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Väster-Rissön, Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517913</v>
+        <v>517898</v>
       </c>
       <c r="R19" t="n">
-        <v>7181387</v>
+        <v>7181203</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2824,18 +2855,32 @@
           <t>2023-09-26</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-09-26</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2859,15 +2904,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112380266</v>
+        <v>112360882</v>
       </c>
       <c r="B20" t="n">
-        <v>89599</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2875,38 +2915,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissön), Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518031</v>
+        <v>517963</v>
       </c>
       <c r="R20" t="n">
-        <v>7181142</v>
+        <v>7181359</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2935,7 +2975,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2945,7 +2985,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2960,26 +3005,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2997,15 +3022,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112382054</v>
+        <v>112360935</v>
       </c>
       <c r="B21" t="n">
-        <v>89599</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,38 +3033,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Väster-Rissön (Väster-Rissön), Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517831</v>
+        <v>517977</v>
       </c>
       <c r="R21" t="n">
-        <v>7181296</v>
+        <v>7181359</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3073,7 +3093,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3083,7 +3103,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3098,26 +3123,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3135,54 +3140,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112379312</v>
+        <v>112360956</v>
       </c>
       <c r="B22" t="n">
-        <v>90335</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Väster-Rissön, Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518066</v>
+        <v>518056</v>
       </c>
       <c r="R22" t="n">
-        <v>7181133</v>
+        <v>7181359</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3221,7 +3221,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3236,26 +3241,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3273,15 +3258,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112381914</v>
+        <v>112361027</v>
       </c>
       <c r="B23" t="n">
-        <v>89649</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3289,38 +3269,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissjön, Väster-Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517911</v>
+        <v>518175</v>
       </c>
       <c r="R23" t="n">
-        <v>7181235</v>
+        <v>7181267</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3349,7 +3329,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3359,7 +3339,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3374,26 +3359,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3411,15 +3376,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112359677</v>
+        <v>112375702</v>
       </c>
       <c r="B24" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3427,16 +3387,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3444,21 +3404,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518387</v>
+        <v>518233</v>
       </c>
       <c r="R24" t="n">
-        <v>7181238</v>
+        <v>7181370</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3485,24 +3456,9 @@
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3534,54 +3490,51 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112359584</v>
+        <v>112374338</v>
       </c>
       <c r="B25" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>230405</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518347</v>
+        <v>518237</v>
       </c>
       <c r="R25" t="n">
-        <v>7181299</v>
+        <v>7181309</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3608,32 +3561,18 @@
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3657,54 +3596,51 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112359401</v>
+        <v>112374377</v>
       </c>
       <c r="B26" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>230405</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518241</v>
+        <v>518273</v>
       </c>
       <c r="R26" t="n">
-        <v>7181299</v>
+        <v>7181305</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3731,32 +3667,18 @@
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3780,54 +3702,51 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112359774</v>
+        <v>112374546</v>
       </c>
       <c r="B27" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>230405</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Väster-Rissjön (Väster-Rissjön), Ås lm</t>
+          <t>Väster-Rissön, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518269</v>
+        <v>518355</v>
       </c>
       <c r="R27" t="n">
-        <v>7181175</v>
+        <v>7181301</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3854,32 +3773,18 @@
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3903,19 +3808,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112375543</v>
+        <v>112374902</v>
       </c>
       <c r="B28" t="n">
-        <v>77745</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3946,10 +3846,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518245</v>
+        <v>518372</v>
       </c>
       <c r="R28" t="n">
-        <v>7181283</v>
+        <v>7181262</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4014,51 +3914,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112377185</v>
+        <v>112375075</v>
       </c>
       <c r="B29" t="n">
-        <v>90335</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>230405</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Väster-Rissön, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518346</v>
+        <v>518408</v>
       </c>
       <c r="R29" t="n">
-        <v>7181224</v>
+        <v>7181227</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4088,53 +3985,24 @@
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4152,19 +4020,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112374546</v>
+        <v>112375105</v>
       </c>
       <c r="B30" t="n">
-        <v>77745</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -4195,10 +4058,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518355</v>
+        <v>518346</v>
       </c>
       <c r="R30" t="n">
-        <v>7181301</v>
+        <v>7181224</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4263,51 +4126,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112377569</v>
+        <v>112375258</v>
       </c>
       <c r="B31" t="n">
-        <v>89649</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>230405</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väster-Rissön (Väster-Rissön), Ås lm</t>
+          <t>Väster-Rissön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518414</v>
+        <v>518263</v>
       </c>
       <c r="R31" t="n">
-        <v>7181238</v>
+        <v>7181219</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4337,53 +4197,24 @@
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4401,19 +4232,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112375105</v>
+        <v>112375286</v>
       </c>
       <c r="B32" t="n">
-        <v>77745</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4444,10 +4270,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518346</v>
+        <v>518066</v>
       </c>
       <c r="R32" t="n">
-        <v>7181224</v>
+        <v>7181134</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4512,19 +4338,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112375258</v>
+        <v>112375371</v>
       </c>
       <c r="B33" t="n">
-        <v>77745</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4555,10 +4376,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518263</v>
+        <v>517859</v>
       </c>
       <c r="R33" t="n">
-        <v>7181219</v>
+        <v>7181249</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4623,19 +4444,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112374338</v>
+        <v>112375418</v>
       </c>
       <c r="B34" t="n">
-        <v>77745</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4666,10 +4482,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518237</v>
+        <v>517913</v>
       </c>
       <c r="R34" t="n">
-        <v>7181309</v>
+        <v>7181388</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4734,51 +4550,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112379024</v>
+        <v>112375476</v>
       </c>
       <c r="B35" t="n">
-        <v>89671</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Väster-Rissön (Väster-Rissön), Ås lm</t>
+          <t>Väster-Rissön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518269</v>
+        <v>517971</v>
       </c>
       <c r="R35" t="n">
-        <v>7181175</v>
+        <v>7181355</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4808,53 +4621,24 @@
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4872,19 +4656,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112375075</v>
+        <v>112375515</v>
       </c>
       <c r="B36" t="n">
-        <v>77745</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4915,10 +4694,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518408</v>
+        <v>518198</v>
       </c>
       <c r="R36" t="n">
-        <v>7181227</v>
+        <v>7181286</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4983,19 +4762,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112374377</v>
+        <v>112375543</v>
       </c>
       <c r="B37" t="n">
-        <v>77745</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -5026,10 +4800,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518273</v>
+        <v>518245</v>
       </c>
       <c r="R37" t="n">
-        <v>7181305</v>
+        <v>7181283</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5091,117 +4865,6 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>112374902</v>
-      </c>
-      <c r="B38" t="n">
-        <v>77745</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>230405</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Väster-Rissön, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>518373</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7181262</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33659-2023 artfynd.xlsx
+++ b/artfynd/A 33659-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -805,6 +810,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112380266</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -938,6 +948,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112382054</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1071,6 +1086,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112377569</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1204,6 +1224,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112381914</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1337,6 +1362,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112382121</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1470,6 +1500,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112377185</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1603,6 +1638,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112379312</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1721,6 +1761,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112359401</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1839,6 +1884,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112359584</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1957,6 +2007,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112359677</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2075,6 +2130,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112359774</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2193,6 +2253,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112359858</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2311,6 +2376,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112359874</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2429,6 +2499,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112360000</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2547,6 +2622,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112360565</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2665,6 +2745,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112360600</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2783,6 +2868,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112360699</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2901,6 +2991,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112360782</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3019,6 +3114,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112360882</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3137,6 +3237,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112360935</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3255,6 +3360,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112360956</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3373,6 +3483,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112361027</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3487,6 +3602,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112375702</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3593,6 +3713,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112374338</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3699,6 +3824,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112374377</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3805,6 +3935,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112374546</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3911,6 +4046,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112374902</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4017,6 +4157,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112375075</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4123,6 +4268,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112375105</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4229,6 +4379,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112375258</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4335,6 +4490,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112375286</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4441,6 +4601,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112375371</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4547,6 +4712,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112375418</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4653,6 +4823,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112375476</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4759,6 +4934,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112375515</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4865,8 +5045,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112375543</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>